--- a/translation/RelTranslate.xlsx
+++ b/translation/RelTranslate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stb/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stb/Documents/Projekte/FYAYC_intern/gitHub/translation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790CFD23-381D-CD4D-A958-D86FA79CBFA2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABA2088-3C0F-BA4D-A979-BD66125431FA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="27960" windowHeight="17540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="24800" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Search Results Details" sheetId="1" r:id="rId1"/>
@@ -578,13 +578,21 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color indexed="8"/>
+            <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>ObjectID:564EF916-58F2-A7E3-A8DD-F42629BD5DA5;
-Class:oracle.dbtools.crest.model.design.logical.Relation</t>
+          <t xml:space="preserve">ObjectID:564EF916-58F2-A7E3-A8DD-F42629BD5DA5;
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Class:oracle.dbtools.crest.model.design.logical.Relation</t>
         </r>
       </text>
     </comment>
@@ -953,7 +961,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="625">
   <si>
     <t>RelTranslate</t>
   </si>
@@ -2788,9 +2796,6 @@
     <t>definiert</t>
   </si>
   <si>
-    <t>*DE* definiert</t>
-  </si>
-  <si>
     <t>test von</t>
   </si>
   <si>
@@ -2825,6 +2830,12 @@
   </si>
   <si>
     <t>partions</t>
+  </si>
+  <si>
+    <t>is</t>
+  </si>
+  <si>
+    <t>defines</t>
   </si>
 </sst>
 </file>
@@ -3298,7 +3309,7 @@
         <v>538</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>94</v>
@@ -3530,7 +3541,7 @@
         <v>559</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>66</v>
@@ -3542,7 +3553,7 @@
         <v>561</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3559,7 +3570,7 @@
         <v>563</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>94</v>
@@ -3571,7 +3582,7 @@
         <v>564</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3617,7 +3628,7 @@
         <v>559</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>66</v>
@@ -3629,7 +3640,7 @@
         <v>561</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3704,7 +3715,7 @@
         <v>547</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>14</v>
@@ -3716,7 +3727,7 @@
         <v>573</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4255,7 +4266,7 @@
         <v>557</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>558</v>
+        <v>623</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>14</v>
@@ -4267,7 +4278,7 @@
         <v>610</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>611</v>
+        <v>624</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4307,25 +4318,25 @@
         <v>128</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>612</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>613</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G40" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="I40" s="2" t="s">
         <v>614</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4394,25 +4405,25 @@
         <v>96</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>58</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4423,25 +4434,25 @@
         <v>24</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4452,25 +4463,25 @@
         <v>52</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4481,25 +4492,25 @@
         <v>54</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>94</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4510,25 +4521,25 @@
         <v>68</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>52</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4539,25 +4550,25 @@
         <v>56</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>124</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4568,25 +4579,25 @@
         <v>56</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4597,25 +4608,25 @@
         <v>118</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4626,25 +4637,25 @@
         <v>20</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>50</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4655,25 +4666,25 @@
         <v>106</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>38</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4684,25 +4695,25 @@
         <v>40</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4713,25 +4724,25 @@
         <v>42</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>126</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4742,25 +4753,25 @@
         <v>88</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4771,25 +4782,25 @@
         <v>28</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>60</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4800,25 +4811,25 @@
         <v>22</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4829,25 +4840,25 @@
         <v>82</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4858,25 +4869,25 @@
         <v>122</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>36</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4887,25 +4898,25 @@
         <v>44</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4916,25 +4927,25 @@
         <v>46</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4945,25 +4956,25 @@
         <v>48</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>110</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
   </sheetData>

--- a/translation/RelTranslate.xlsx
+++ b/translation/RelTranslate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stb/Documents/Projekte/FYAYC_intern/gitHub/translation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABA2088-3C0F-BA4D-A979-BD66125431FA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3457089A-13FF-EA4F-B5A6-3C845D0E475A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="24800" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="28480" windowHeight="17940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Search Results Details" sheetId="1" r:id="rId1"/>
@@ -961,7 +961,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="624">
   <si>
     <t>RelTranslate</t>
   </si>
@@ -2589,69 +2589,36 @@
     <t>verwendet</t>
   </si>
   <si>
-    <t>*DE* verwendet</t>
-  </si>
-  <si>
     <t>besitzt</t>
   </si>
   <si>
-    <t>*DE* besitzt</t>
-  </si>
-  <si>
     <t>gehört</t>
   </si>
   <si>
-    <t>*DE* gehört</t>
-  </si>
-  <si>
     <t>umfasst</t>
   </si>
   <si>
-    <t>*DE* umfasst</t>
-  </si>
-  <si>
     <t>lebt in</t>
   </si>
   <si>
-    <t>*DE* lebt in</t>
-  </si>
-  <si>
     <t>bedient</t>
   </si>
   <si>
-    <t>*DE* bedient</t>
-  </si>
-  <si>
     <t>bedient von</t>
   </si>
   <si>
-    <t>*DE* bedient von</t>
-  </si>
-  <si>
     <t>tritt auf als</t>
   </si>
   <si>
-    <t>*DE* tritt auf als</t>
-  </si>
-  <si>
     <t>ist</t>
   </si>
   <si>
-    <t>*DE* ist</t>
-  </si>
-  <si>
     <t>unterteilt in</t>
   </si>
   <si>
-    <t>*DE* unterteilt in</t>
-  </si>
-  <si>
     <t>unterteilt</t>
   </si>
   <si>
-    <t>*DE* unterteilt</t>
-  </si>
-  <si>
     <t>fasst zusammen</t>
   </si>
   <si>
@@ -2661,138 +2628,72 @@
     <t>offiziell verwendet in</t>
   </si>
   <si>
-    <t>*DE* offiziell verwendet in</t>
-  </si>
-  <si>
     <t>verwendet offiziell</t>
   </si>
   <si>
-    <t>*DE* verwendet offiziell</t>
-  </si>
-  <si>
     <t>beschäftigt</t>
   </si>
   <si>
-    <t>*DE* beschäftigt</t>
-  </si>
-  <si>
     <t>arbeitet für</t>
   </si>
   <si>
-    <t>*DE* arbeitet für</t>
-  </si>
-  <si>
     <t>liegt in</t>
   </si>
   <si>
     <t>bekannt als</t>
   </si>
   <si>
-    <t>*DE* bekannt als</t>
-  </si>
-  <si>
     <t>erreichbar mittels</t>
   </si>
   <si>
-    <t>*DE* erreichbar mittels</t>
-  </si>
-  <si>
     <t>gilt für</t>
   </si>
   <si>
-    <t>*DE* gilt für</t>
-  </si>
-  <si>
     <t>nimmt wahr</t>
   </si>
   <si>
-    <t>*DE* nimmt wahr</t>
-  </si>
-  <si>
     <t>wahrgenommen von</t>
   </si>
   <si>
-    <t>*DE* wahrgenommen von</t>
-  </si>
-  <si>
     <t>betreut</t>
   </si>
   <si>
-    <t>*DE* betreut</t>
-  </si>
-  <si>
     <t>betreut von</t>
   </si>
   <si>
-    <t>*DE* betreut von</t>
-  </si>
-  <si>
     <t>vertreten an</t>
   </si>
   <si>
-    <t>*DE* vertreten an</t>
-  </si>
-  <si>
     <t>betrieben von</t>
   </si>
   <si>
-    <t>*DE* betrieben von</t>
-  </si>
-  <si>
     <t>organisiert in</t>
   </si>
   <si>
-    <t>*DE* organisiert in</t>
-  </si>
-  <si>
     <t>organisiert</t>
   </si>
   <si>
-    <t>*DE* organisiert</t>
-  </si>
-  <si>
     <t>verbunden mit</t>
   </si>
   <si>
-    <t>*DE* verbunden mit</t>
-  </si>
-  <si>
     <t>verbunden mit [T]</t>
   </si>
   <si>
-    <t>*DE* verbunden mit [T]</t>
-  </si>
-  <si>
     <t>besitzt physisch</t>
   </si>
   <si>
-    <t>*DE* besitzt physisch</t>
-  </si>
-  <si>
     <t>physisch bei</t>
   </si>
   <si>
-    <t>*DE* physisch bei</t>
-  </si>
-  <si>
     <t>besitzt rechtlich</t>
   </si>
   <si>
-    <t>*DE* besitzt rechtlich</t>
-  </si>
-  <si>
     <t>betreut direkt</t>
   </si>
   <si>
-    <t>*DE* betreut direkt</t>
-  </si>
-  <si>
     <t>direkt betreut von</t>
   </si>
   <si>
-    <t>*DE* direkt betreut von</t>
-  </si>
-  <si>
     <t>definiert</t>
   </si>
   <si>
@@ -2836,6 +2737,102 @@
   </si>
   <si>
     <t>defines</t>
+  </si>
+  <si>
+    <t>**besitzt</t>
+  </si>
+  <si>
+    <t>**umfasst</t>
+  </si>
+  <si>
+    <t>**utilised</t>
+  </si>
+  <si>
+    <t>**heard</t>
+  </si>
+  <si>
+    <t>**lives in</t>
+  </si>
+  <si>
+    <t>**attended</t>
+  </si>
+  <si>
+    <t>**operated by</t>
+  </si>
+  <si>
+    <t>**occurs as</t>
+  </si>
+  <si>
+    <t>**is</t>
+  </si>
+  <si>
+    <t>**officially used in</t>
+  </si>
+  <si>
+    <t>**officially used</t>
+  </si>
+  <si>
+    <t>**preoccupied</t>
+  </si>
+  <si>
+    <t>**works for</t>
+  </si>
+  <si>
+    <t>**subdivided into</t>
+  </si>
+  <si>
+    <t>**subdivided</t>
+  </si>
+  <si>
+    <t>**known as</t>
+  </si>
+  <si>
+    <t>**achievable by</t>
+  </si>
+  <si>
+    <t>**applies to</t>
+  </si>
+  <si>
+    <t>**perceives</t>
+  </si>
+  <si>
+    <t>**perceived by</t>
+  </si>
+  <si>
+    <t>**supervised</t>
+  </si>
+  <si>
+    <t>**supervised by</t>
+  </si>
+  <si>
+    <t>**represented at</t>
+  </si>
+  <si>
+    <t>**organized in</t>
+  </si>
+  <si>
+    <t>**organised</t>
+  </si>
+  <si>
+    <t>**associated with</t>
+  </si>
+  <si>
+    <t>**connected to [T]</t>
+  </si>
+  <si>
+    <t>**possesses physical</t>
+  </si>
+  <si>
+    <t>**physically at</t>
+  </si>
+  <si>
+    <t>**legally owns</t>
+  </si>
+  <si>
+    <t>**supervised directly</t>
+  </si>
+  <si>
+    <t>**directly supervised by</t>
   </si>
 </sst>
 </file>
@@ -2911,7 +2908,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2922,6 +2919,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3254,17 +3255,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -3308,20 +3309,20 @@
       <c r="D5" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="E5" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>542</v>
+      <c r="I5" s="4" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3332,25 +3333,25 @@
         <v>86</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="H6" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>546</v>
+      <c r="I6" s="4" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3361,25 +3362,25 @@
         <v>78</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="F7" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>550</v>
+      <c r="G7" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3390,25 +3391,25 @@
         <v>136</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="F8" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>554</v>
+      <c r="G8" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3419,25 +3420,25 @@
         <v>72</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="F9" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>558</v>
+      <c r="G9" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3448,25 +3449,25 @@
         <v>60</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="F10" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>558</v>
+      <c r="G10" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3477,25 +3478,25 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="F11" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>558</v>
+      <c r="G11" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3506,25 +3507,25 @@
         <v>88</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="F12" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>558</v>
+      <c r="G12" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3535,25 +3536,25 @@
         <v>94</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="F13" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>618</v>
+      <c r="G13" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3564,25 +3565,25 @@
         <v>96</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="F14" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>620</v>
+      <c r="G14" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3593,25 +3594,25 @@
         <v>124</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="F15" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>568</v>
+      <c r="G15" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3622,25 +3623,25 @@
         <v>66</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="F16" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>622</v>
+      <c r="G16" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3651,25 +3652,25 @@
         <v>86</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="F17" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>572</v>
+      <c r="G17" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3680,25 +3681,25 @@
         <v>124</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="F18" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>562</v>
+      <c r="G18" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3709,25 +3710,25 @@
         <v>112</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="F19" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>620</v>
+      <c r="G19" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3738,25 +3739,25 @@
         <v>102</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>574</v>
+        <v>559</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="F20" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>558</v>
+      <c r="G20" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3767,25 +3768,25 @@
         <v>72</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="F21" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>579</v>
+      <c r="G21" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3796,25 +3797,25 @@
         <v>20</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>580</v>
+        <v>562</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="F22" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>583</v>
+      <c r="G22" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3825,25 +3826,25 @@
         <v>130</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="F23" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>558</v>
+      <c r="G23" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3854,25 +3855,25 @@
         <v>74</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>584</v>
+        <v>564</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="F24" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>587</v>
+      <c r="G24" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3883,25 +3884,25 @@
         <v>132</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="F25" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>558</v>
+      <c r="G25" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3912,25 +3913,25 @@
         <v>132</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="F26" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>558</v>
+      <c r="G26" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3941,25 +3942,25 @@
         <v>74</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="F27" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>556</v>
+      <c r="G27" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3970,25 +3971,25 @@
         <v>70</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F28" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>552</v>
+      <c r="G28" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3999,25 +4000,25 @@
         <v>86</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>588</v>
+        <v>566</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="F29" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>591</v>
+      <c r="G29" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4028,25 +4029,25 @@
         <v>90</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>578</v>
+        <v>561</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="F30" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>577</v>
+      <c r="G30" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4057,25 +4058,25 @@
         <v>86</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>592</v>
+        <v>568</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="F31" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>595</v>
+      <c r="G31" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4086,25 +4087,25 @@
         <v>102</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>596</v>
+        <v>570</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="F32" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>599</v>
+      <c r="G32" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4115,25 +4116,25 @@
         <v>106</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="F33" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="G33" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>562</v>
+      <c r="G33" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4144,25 +4145,25 @@
         <v>22</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>600</v>
+        <v>572</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="F34" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>603</v>
+      <c r="G34" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4173,25 +4174,25 @@
         <v>60</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>604</v>
+        <v>574</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="F35" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="G35" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>546</v>
+      <c r="G35" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4202,25 +4203,25 @@
         <v>20</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>606</v>
+        <v>575</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="F36" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="F36" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="G36" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>609</v>
+      <c r="G36" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4231,25 +4232,25 @@
         <v>132</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>606</v>
+        <v>575</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="F37" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="G37" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>609</v>
+      <c r="G37" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4260,25 +4261,25 @@
         <v>90</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="F38" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="F38" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>624</v>
+      <c r="G38" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4289,25 +4290,25 @@
         <v>90</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>578</v>
+        <v>561</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="F39" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="F39" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G39" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>577</v>
+      <c r="G39" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4318,25 +4319,25 @@
         <v>128</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>611</v>
+        <v>578</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="F40" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G40" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>614</v>
+      <c r="G40" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4347,25 +4348,25 @@
         <v>72</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>580</v>
+        <v>562</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="F41" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="F41" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="G41" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>583</v>
+      <c r="G41" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4376,25 +4377,25 @@
         <v>72</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="F42" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="G42" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>558</v>
+      <c r="G42" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4405,26 +4406,18 @@
         <v>96</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F43" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>615</v>
-      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
     </row>
     <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
@@ -4434,26 +4427,18 @@
         <v>24</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F44" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G44" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>615</v>
-      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
     </row>
     <row r="45" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
@@ -4463,26 +4448,18 @@
         <v>52</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F45" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G45" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>615</v>
-      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
     </row>
     <row r="46" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
@@ -4492,26 +4469,18 @@
         <v>54</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F46" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G46" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>615</v>
-      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
     </row>
     <row r="47" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
@@ -4521,26 +4490,18 @@
         <v>68</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F47" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="G47" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>615</v>
-      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
     </row>
     <row r="48" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
@@ -4550,26 +4511,18 @@
         <v>56</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F48" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="G48" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>615</v>
-      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
     </row>
     <row r="49" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
@@ -4579,26 +4532,18 @@
         <v>56</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F49" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G49" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>615</v>
-      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
     </row>
     <row r="50" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
@@ -4608,26 +4553,18 @@
         <v>118</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F50" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G50" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>615</v>
-      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
     </row>
     <row r="51" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
@@ -4637,26 +4574,18 @@
         <v>20</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F51" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G51" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>615</v>
-      </c>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
     </row>
     <row r="52" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
@@ -4666,26 +4595,18 @@
         <v>106</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F52" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G52" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>615</v>
-      </c>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
     </row>
     <row r="53" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
@@ -4695,26 +4616,18 @@
         <v>40</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F53" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="G53" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>615</v>
-      </c>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
     </row>
     <row r="54" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
@@ -4724,26 +4637,18 @@
         <v>42</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F54" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="G54" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>615</v>
-      </c>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
     </row>
     <row r="55" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
@@ -4753,26 +4658,18 @@
         <v>88</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F55" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G55" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>615</v>
-      </c>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
     </row>
     <row r="56" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
@@ -4782,26 +4679,18 @@
         <v>28</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F56" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G56" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>615</v>
-      </c>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
     </row>
     <row r="57" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
@@ -4811,26 +4700,18 @@
         <v>22</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F57" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G57" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>615</v>
-      </c>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
     </row>
     <row r="58" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
@@ -4840,26 +4721,18 @@
         <v>82</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F58" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G58" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>615</v>
-      </c>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
     </row>
     <row r="59" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
@@ -4869,26 +4742,18 @@
         <v>122</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F59" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G59" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>615</v>
-      </c>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
     </row>
     <row r="60" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
@@ -4898,26 +4763,18 @@
         <v>44</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F60" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="G60" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>615</v>
-      </c>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
     </row>
     <row r="61" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
@@ -4927,26 +4784,18 @@
         <v>46</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F61" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="G61" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>615</v>
-      </c>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
     </row>
     <row r="62" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
@@ -4956,26 +4805,18 @@
         <v>48</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F62" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G62" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>615</v>
-      </c>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
